--- a/data/mini-affirmations.xlsx
+++ b/data/mini-affirmations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Κεντρική Επιτροπή Διαιτησίας\ΣΕΜΙΝΑΡΙΑ-ΕΞΕΤΑΣΕΙΣ\2026\WKF EXAMINATIONS 2026\ΕΦΑΡΜΟΓΗ ds\MermaidApp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7DCD26-A45A-417F-BEBB-14065D0D0134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76715904-52CC-4F24-94C0-C489A637A94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
